--- a/consulting_forms/004_adhd_consultation_form--consulting_forms.xlsx
+++ b/consulting_forms/004_adhd_consultation_form--consulting_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1030,8 +1030,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="48" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Never', 'value': 'never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely', 'value': 'rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes',_'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes', 'value': 'sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'often',_'value':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Often', 'value': 'often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_often',_'value':_'very_often'}</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very Often', 'value': 'very_often'}</t>
+          <t>Very Often</t>
         </is>
       </c>
     </row>
@@ -1144,12 +1144,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Never', 'value': 'never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely', 'value': 'rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1178,12 +1178,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes',_'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes', 'value': 'sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1195,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'often',_'value':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Often', 'value': 'often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1212,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'very_often',_'value':_'very_often'}</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Very Often', 'value': 'very_often'}</t>
+          <t>Very Often</t>
         </is>
       </c>
     </row>
@@ -1229,12 +1229,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'never',_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Never', 'value': 'never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1246,12 +1246,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'rarely',_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely', 'value': 'rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1263,12 +1263,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes',_'value':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes', 'value': 'sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1280,12 +1280,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'often',_'value':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Often', 'value': 'often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1297,12 +1297,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'very_often',_'value':_'very_often'}</t>
+          <t>very_often</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Very Often', 'value': 'very_often'}</t>
+          <t>Very Often</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all',_'value':_'none'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all', 'value': 'none'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'mildly',_'value':_'mild'}</t>
+          <t>mildly</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Mildly', 'value': 'mild'}</t>
+          <t>Mildly</t>
         </is>
       </c>
     </row>
@@ -1348,12 +1348,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'moderately',_'value':_'moderate'}</t>
+          <t>moderately</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Moderately', 'value': 'moderate'}</t>
+          <t>Moderately</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1365,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'severely',_'value':_'severe'}</t>
+          <t>severely</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Severely', 'value': 'severe'}</t>
+          <t>Severely</t>
         </is>
       </c>
     </row>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all',_'value':_'none'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all', 'value': 'none'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1399,12 +1399,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'mildly',_'value':_'mild'}</t>
+          <t>mildly</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Mildly', 'value': 'mild'}</t>
+          <t>Mildly</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'moderately',_'value':_'moderate'}</t>
+          <t>moderately</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Moderately', 'value': 'moderate'}</t>
+          <t>Moderately</t>
         </is>
       </c>
     </row>
@@ -1433,12 +1433,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'severely',_'value':_'severe'}</t>
+          <t>severely</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Severely', 'value': 'severe'}</t>
+          <t>Severely</t>
         </is>
       </c>
     </row>
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1467,12 +1467,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1518,12 +1518,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'unsure',_'value':_'unsure'}</t>
+          <t>unsure</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Unsure', 'value': 'unsure'}</t>
+          <t>Unsure</t>
         </is>
       </c>
     </row>
@@ -1535,12 +1535,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'phone',_'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Phone', 'value': 'phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'email',_'value':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Email', 'value': 'email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
